--- a/public/downloads/원가분석_템플릿.xlsx
+++ b/public/downloads/원가분석_템플릿.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="216">
   <si>
     <t>📘 우리 매장 · 메뉴 원가 분석서</t>
   </si>
@@ -134,16 +134,28 @@
     <t>해당 메뉴의 재료비 전부 합계 (⑤ 시트 SUMIF)</t>
   </si>
   <si>
+    <t>공급가액</t>
+  </si>
+  <si>
+    <t>판매가 ÷ 부가세 계수 — 판매가가 부가세 포함이면 실제로 매장에 남는 금액</t>
+  </si>
+  <si>
     <t>고정비 배분</t>
   </si>
   <si>
-    <t>판매가 × (배분대상 고정비 ÷ 월 추정매출) — 판매가에 비례해 배분</t>
+    <t>공급가액 × (배분대상 고정비 ÷ 월 매출 공급가액)</t>
   </si>
   <si>
     <t>총원가 / 마진</t>
   </si>
   <si>
-    <t>총원가 = 식재료 원가 + 고정비 배분,  마진 = 판매가 − 총원가</t>
+    <t>총원가 = 식재료 원가 + 고정비 배분,  마진 = 공급가액 − 총원가</t>
+  </si>
+  <si>
+    <t>원가율·마진율</t>
+  </si>
+  <si>
+    <t>모두 판매가가 아니라 공급가액을 기준으로 계산합니다 (부가세는 매출이 아니므로)</t>
   </si>
   <si>
     <t>▸  꼭 알아두실 점</t>
@@ -224,9 +236,6 @@
     <t>총원가</t>
   </si>
   <si>
-    <t>마진 합계</t>
-  </si>
-  <si>
     <t>마진율</t>
   </si>
   <si>
@@ -254,10 +263,10 @@
     <t>원가율 하위 10 (효자 메뉴)</t>
   </si>
   <si>
-    <t>레시피북 87개 메뉴 전체. 판매가(노란 셀)만 고치면 원가율·마진이 즉시 다시 계산됩니다.</t>
-  </si>
-  <si>
-    <t>💡  식재료원가 = ⑤ 레시피 상세의 합계 |  고정비 배분 = 판매가 × 고정비 배분율 |  총원가 = 식재료원가 + 고정비 배분 |  판정 = 식재료 원가율 기준</t>
+    <t>메뉴 3개 전체. 판매가(노란 셀)만 고치면 원가율·마진이 즉시 다시 계산됩니다.</t>
+  </si>
+  <si>
+    <t>💡  공급가액 = 판매가 ÷ 부가세 계수 (③ 시트).  원가율·마진은 모두 공급가액 기준입니다.  고정비 배분 = 공급가액 × 고정비 배분율.  총원가 = 식재료원가 + 고정비 배분.</t>
   </si>
   <si>
     <t>No.</t>
@@ -543,16 +552,40 @@
     <t>「배분 포함」인 항목만 합산 → 메뉴 원가에 반영</t>
   </si>
   <si>
-    <t>▸  배분·판정 기준 설정</t>
+    <t>▸  부가세 · 배분 · 판정 기준 설정</t>
+  </si>
+  <si>
+    <t>부가세 처리</t>
+  </si>
+  <si>
+    <t>판매가가 손님이 내는 금액이면 「포함」, 공급가액이면 「별도」</t>
+  </si>
+  <si>
+    <t>부가세율</t>
+  </si>
+  <si>
+    <t>「포함」일 때만 사용 (면세면 0%)</t>
+  </si>
+  <si>
+    <t>부가세 계수</t>
+  </si>
+  <si>
+    <t>판매가 ÷ 이 값 = 공급가액</t>
   </si>
   <si>
     <t>월 추정매출(원)</t>
   </si>
   <si>
-    <t>배달 포함 월 총매출 추정치</t>
-  </si>
-  <si>
-    <t>= 배분 대상 합계 ÷ 월 추정매출 (매출 1원당 고정비)</t>
+    <t>배달 포함 월 총매출 (부가세 처리 기준과 동일하게 입력)</t>
+  </si>
+  <si>
+    <t>월 매출 (공급가액)</t>
+  </si>
+  <si>
+    <t>= 월 추정매출 ÷ 부가세 계수</t>
+  </si>
+  <si>
+    <t>= 배분 대상 합계 ÷ 월 매출(공급가액)</t>
   </si>
   <si>
     <t>목표 식재료 원가율</t>
@@ -643,13 +676,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000000"/>
     <numFmt numFmtId="166" formatCode="#,##0.##"/>
     <numFmt numFmtId="167" formatCode="#,##0.000"/>
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
     <numFmt numFmtId="169" formatCode="#,##0.###"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
   <fonts count="33" x14ac:knownFonts="1">
     <font>
@@ -962,7 +996,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1095,6 +1129,7 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="21" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1153,6 +1188,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
+    <xf numFmtId="170" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -1531,7 +1567,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="19" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1724,35 +1760,35 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+    <row r="27" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" ht="46" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
+      <c r="C27" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="7" t="s">
+    </row>
+    <row r="28" ht="34" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="30" ht="34" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="4" t="s">
+      <c r="C28" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="5" t="s">
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="31" ht="34" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="4" t="s">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="31" ht="46" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1762,6 +1798,22 @@
       </c>
       <c r="C32" s="5" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1771,7 +1823,7 @@
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -1815,7 +1867,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1830,23 +1882,23 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="15" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="15" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="15" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="15" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K4" s="15"/>
     </row>
@@ -1856,25 +1908,25 @@
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="17">
-        <f>IF('④ 메뉴 원가표'!$D$9&gt;0,'④ 메뉴 원가표'!$E$9/'④ 메뉴 원가표'!$D$9,0)</f>
+        <f>IF('④ 메뉴 원가표'!$E$9&gt;0,'④ 메뉴 원가표'!$F$9/'④ 메뉴 원가표'!$E$9,0)</f>
       </c>
       <c r="E5" s="17"/>
       <c r="F5" s="17">
-        <f>IF('④ 메뉴 원가표'!$D$9&gt;0,'④ 메뉴 원가표'!$H$9/'④ 메뉴 원가표'!$D$9,0)</f>
+        <f>IF('④ 메뉴 원가표'!$E$9&gt;0,'④ 메뉴 원가표'!$I$9/'④ 메뉴 원가표'!$E$9,0)</f>
       </c>
       <c r="G5" s="17"/>
       <c r="H5" s="17">
-        <f>IF('④ 메뉴 원가표'!$D$9&gt;0,('④ 메뉴 원가표'!$D$9-'④ 메뉴 원가표'!$H$9)/'④ 메뉴 원가표'!$D$9,0)</f>
+        <f>IF('④ 메뉴 원가표'!$E$9&gt;0,('④ 메뉴 원가표'!$E$9-'④ 메뉴 원가표'!$I$9)/'④ 메뉴 원가표'!$E$9,0)</f>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17">
-        <f>'③ 고정비 설정'!$C$16</f>
+        <f>'③ 고정비 설정'!$C$20</f>
       </c>
       <c r="K5" s="17"/>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1893,7 +1945,7 @@
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="19">
-        <f>COUNTIF('④ 메뉴 원가표'!$L$6:$L$8,"*양호*")</f>
+        <f>COUNTIF('④ 메뉴 원가표'!$M$6:$M$8,"*양호*")</f>
       </c>
       <c r="E8" s="20">
         <f>IF(COUNTA('④ 메뉴 원가표'!$C$6:$C$8)&gt;0,D8/COUNTA('④ 메뉴 원가표'!$C$6:$C$8),0)</f>
@@ -1905,7 +1957,7 @@
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="22">
-        <f>COUNTIF('④ 메뉴 원가표'!$L$6:$L$8,"*주의*")</f>
+        <f>COUNTIF('④ 메뉴 원가표'!$M$6:$M$8,"*주의*")</f>
       </c>
       <c r="E9" s="23">
         <f>IF(COUNTA('④ 메뉴 원가표'!$C$6:$C$8)&gt;0,D9/COUNTA('④ 메뉴 원가표'!$C$6:$C$8),0)</f>
@@ -1917,7 +1969,7 @@
       </c>
       <c r="C10" s="24"/>
       <c r="D10" s="25">
-        <f>COUNTIF('④ 메뉴 원가표'!$L$6:$L$8,"*과다*")</f>
+        <f>COUNTIF('④ 메뉴 원가표'!$M$6:$M$8,"*과다*")</f>
       </c>
       <c r="E10" s="26">
         <f>IF(COUNTA('④ 메뉴 원가표'!$C$6:$C$8)&gt;0,D10/COUNTA('④ 메뉴 원가표'!$C$6:$C$8),0)</f>
@@ -1925,11 +1977,11 @@
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="27" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C11" s="27"/>
       <c r="D11" s="28">
-        <f>COUNTIF('④ 메뉴 원가표'!$L$6:$L$8,"*판매가*")</f>
+        <f>COUNTIF('④ 메뉴 원가표'!$M$6:$M$8,"*판매가*")</f>
       </c>
       <c r="E11" s="29">
         <f>IF(COUNTA('④ 메뉴 원가표'!$C$6:$C$8)&gt;0,D11/COUNTA('④ 메뉴 원가표'!$C$6:$C$8),0)</f>
@@ -1937,7 +1989,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1952,42 +2004,42 @@
     </row>
     <row r="14" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H14" s="30" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I14" s="30" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J14" s="30" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K14" s="30" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C15" s="32">
         <f>COUNTIF('④ 메뉴 원가표'!$B$6:$B$8,"🍳 메인 요리")</f>
@@ -1998,25 +2050,25 @@
       <c r="E15" s="33">
         <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍳 메인 요리",'④ 메뉴 원가표'!$E$6:$E$8)</f>
       </c>
-      <c r="F15" s="34">
-        <f>IF(D15&gt;0,E15/D15,"")</f>
-      </c>
-      <c r="G15" s="33">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍳 메인 요리",'④ 메뉴 원가표'!$G$6:$G$8)</f>
+      <c r="F15" s="33">
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍳 메인 요리",'④ 메뉴 원가표'!$F$6:$F$8)</f>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15&gt;0,F15/E15,"")</f>
       </c>
       <c r="H15" s="33">
         <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍳 메인 요리",'④ 메뉴 원가표'!$H$6:$H$8)</f>
       </c>
       <c r="I15" s="33">
-        <f>IF(D15&gt;0,D15-H15,"")</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍳 메인 요리",'④ 메뉴 원가표'!$I$6:$I$8)</f>
       </c>
       <c r="J15" s="35">
-        <f>IF(D15&gt;0,I15/D15,"")</f>
+        <f>IF(E15&gt;0,(E15-I15)/E15,"")</f>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C16" s="37">
         <f>COUNTIF('④ 메뉴 원가표'!$B$6:$B$8,"🥗 사이드")</f>
@@ -2027,25 +2079,25 @@
       <c r="E16" s="38">
         <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🥗 사이드",'④ 메뉴 원가표'!$E$6:$E$8)</f>
       </c>
-      <c r="F16" s="39">
-        <f>IF(D16&gt;0,E16/D16,"")</f>
-      </c>
-      <c r="G16" s="38">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🥗 사이드",'④ 메뉴 원가표'!$G$6:$G$8)</f>
+      <c r="F16" s="38">
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🥗 사이드",'④ 메뉴 원가표'!$F$6:$F$8)</f>
+      </c>
+      <c r="G16" s="39">
+        <f>IF(E16&gt;0,F16/E16,"")</f>
       </c>
       <c r="H16" s="38">
         <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🥗 사이드",'④ 메뉴 원가표'!$H$6:$H$8)</f>
       </c>
       <c r="I16" s="38">
-        <f>IF(D16&gt;0,D16-H16,"")</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🥗 사이드",'④ 메뉴 원가표'!$I$6:$I$8)</f>
       </c>
       <c r="J16" s="40">
-        <f>IF(D16&gt;0,I16/D16,"")</f>
+        <f>IF(E16&gt;0,(E16-I16)/E16,"")</f>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="31" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C17" s="32">
         <f>COUNTIF('④ 메뉴 원가표'!$B$6:$B$8,"🍽 세트메뉴")</f>
@@ -2056,25 +2108,25 @@
       <c r="E17" s="33">
         <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍽 세트메뉴",'④ 메뉴 원가표'!$E$6:$E$8)</f>
       </c>
-      <c r="F17" s="34">
-        <f>IF(D17&gt;0,E17/D17,"")</f>
-      </c>
-      <c r="G17" s="33">
-        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍽 세트메뉴",'④ 메뉴 원가표'!$G$6:$G$8)</f>
+      <c r="F17" s="33">
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍽 세트메뉴",'④ 메뉴 원가표'!$F$6:$F$8)</f>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17&gt;0,F17/E17,"")</f>
       </c>
       <c r="H17" s="33">
         <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍽 세트메뉴",'④ 메뉴 원가표'!$H$6:$H$8)</f>
       </c>
       <c r="I17" s="33">
-        <f>IF(D17&gt;0,D17-H17,"")</f>
+        <f>SUMIF('④ 메뉴 원가표'!$B$6:$B$8,"🍽 세트메뉴",'④ 메뉴 원가표'!$I$6:$I$8)</f>
       </c>
       <c r="J17" s="35">
-        <f>IF(D17&gt;0,I17/D17,"")</f>
+        <f>IF(E17&gt;0,(E17-I17)/E17,"")</f>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B19" s="41"/>
       <c r="C19" s="41"/>
@@ -2089,33 +2141,33 @@
     </row>
     <row r="20" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="30" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G20" s="30" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H20" s="42" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I20" s="42"/>
       <c r="J20" s="42"/>
       <c r="K20" s="30" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
@@ -2123,28 +2175,28 @@
         <v>1</v>
       </c>
       <c r="C21" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,1),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,1),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="D21" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,1),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,1),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="E21" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$E$6:$E$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,1),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,1),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="F21" s="45">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,1),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,1),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="G21" s="46" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H21" s="43">
         <v>1</v>
       </c>
       <c r="I21" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,1),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,1),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="J21" s="47">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,1),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,1),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
@@ -2152,28 +2204,28 @@
         <v>2</v>
       </c>
       <c r="C22" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,2),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,2),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="D22" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,2),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,2),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="E22" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$E$6:$E$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,2),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,2),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="F22" s="50">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,2),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,2),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="G22" s="46" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H22" s="48">
         <v>2</v>
       </c>
       <c r="I22" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,2),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,2),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="J22" s="51">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,2),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,2),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
@@ -2181,28 +2233,28 @@
         <v>3</v>
       </c>
       <c r="C23" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,3),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,3),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="D23" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,3),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,3),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="E23" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$E$6:$E$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,3),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,3),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="F23" s="45">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,3),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,3),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="G23" s="46" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H23" s="43">
         <v>3</v>
       </c>
       <c r="I23" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,3),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,3),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="J23" s="47">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,3),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,3),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
@@ -2210,28 +2262,28 @@
         <v>4</v>
       </c>
       <c r="C24" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,4),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,4),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="D24" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,4),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,4),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="E24" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$E$6:$E$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,4),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,4),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="F24" s="50">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,4),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,4),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="G24" s="46" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H24" s="48">
         <v>4</v>
       </c>
       <c r="I24" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,4),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,4),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="J24" s="51">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,4),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,4),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
@@ -2239,28 +2291,28 @@
         <v>5</v>
       </c>
       <c r="C25" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,5),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,5),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="D25" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,5),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,5),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="E25" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$E$6:$E$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,5),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,5),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="F25" s="45">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,5),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,5),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="G25" s="46" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H25" s="43">
         <v>5</v>
       </c>
       <c r="I25" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,5),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,5),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="J25" s="47">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,5),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,5),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
@@ -2268,28 +2320,28 @@
         <v>6</v>
       </c>
       <c r="C26" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,6),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,6),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="D26" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,6),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,6),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="E26" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$E$6:$E$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,6),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,6),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="F26" s="50">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,6),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,6),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="G26" s="46" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H26" s="48">
         <v>6</v>
       </c>
       <c r="I26" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,6),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,6),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="J26" s="51">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,6),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,6),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
@@ -2297,28 +2349,28 @@
         <v>7</v>
       </c>
       <c r="C27" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,7),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,7),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="D27" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,7),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,7),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="E27" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$E$6:$E$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,7),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,7),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="F27" s="45">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,7),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,7),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="G27" s="46" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H27" s="43">
         <v>7</v>
       </c>
       <c r="I27" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,7),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,7),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="J27" s="47">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,7),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,7),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
@@ -2326,28 +2378,28 @@
         <v>8</v>
       </c>
       <c r="C28" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,8),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,8),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="D28" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,8),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,8),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="E28" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$E$6:$E$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,8),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,8),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="F28" s="50">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,8),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,8),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="G28" s="46" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H28" s="48">
         <v>8</v>
       </c>
       <c r="I28" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,8),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,8),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="J28" s="51">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,8),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,8),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
@@ -2355,28 +2407,28 @@
         <v>9</v>
       </c>
       <c r="C29" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,9),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,9),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="D29" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,9),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,9),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="E29" s="33">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$E$6:$E$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,9),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,9),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="F29" s="45">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,9),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,9),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="G29" s="46" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H29" s="43">
         <v>9</v>
       </c>
       <c r="I29" s="44">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,9),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,9),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="J29" s="47">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,9),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,9),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
@@ -2384,28 +2436,28 @@
         <v>10</v>
       </c>
       <c r="C30" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,10),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,10),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="D30" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,10),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$D$6:$D$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,10),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="E30" s="38">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$E$6:$E$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,10),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,10),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="F30" s="50">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(LARGE('④ 메뉴 원가표'!$M$6:$M$8,10),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(LARGE('④ 메뉴 원가표'!$N$6:$N$8,10),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="G30" s="46" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H30" s="48">
         <v>10</v>
       </c>
       <c r="I30" s="49">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,10),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$C$6:$C$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,10),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
       <c r="J30" s="51">
-        <f>IFERROR(INDEX('④ 메뉴 원가표'!$F$6:$F$8,MATCH(SMALL('④ 메뉴 원가표'!$M$6:$M$8,10),'④ 메뉴 원가표'!$M$6:$M$8,0)),"")</f>
+        <f>IFERROR(INDEX('④ 메뉴 원가표'!$G$6:$G$8,MATCH(SMALL('④ 메뉴 원가표'!$N$6:$N$8,10),'④ 메뉴 원가표'!$N$6:$N$8,0)),"")</f>
       </c>
     </row>
   </sheetData>
@@ -2431,7 +2483,7 @@
     <mergeCell ref="A19:K19"/>
     <mergeCell ref="H20:J20"/>
   </mergeCells>
-  <conditionalFormatting sqref="F15:F17">
+  <conditionalFormatting sqref="G15:G17">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -2453,7 +2505,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="19" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2466,10 +2518,10 @@
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="9" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" ht="34" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2485,10 +2537,11 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2502,10 +2555,11 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
@@ -2519,226 +2573,242 @@
       <c r="K3" s="52"/>
       <c r="L3" s="52"/>
       <c r="M3" s="52"/>
-    </row>
-    <row r="5" ht="26" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" s="52"/>
+    </row>
+    <row r="5" ht="26" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="L5" s="30" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="M5" s="30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="N5" s="30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="53">
         <v>1</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D6" s="55">
         <v>9000</v>
       </c>
       <c r="E6" s="56">
+        <f>ROUND($D6/'③ 고정비 설정'!$C$17,0)</f>
+      </c>
+      <c r="F6" s="57">
         <f>ROUND(SUMIF('⑤ 레시피 상세'!$B$6:$B$20,$C6,'⑤ 레시피 상세'!$K$6:$K$20),1)</f>
       </c>
-      <c r="F6" s="57">
-        <f>IF($D6&gt;0,$E6/$D6,"")</f>
-      </c>
-      <c r="G6" s="56">
-        <f>ROUND($D6*'③ 고정비 설정'!$C$16,0)</f>
-      </c>
-      <c r="H6" s="56">
-        <f>ROUND($E6+$G6,0)</f>
-      </c>
-      <c r="I6" s="58">
-        <f>IF($D6&gt;0,$H6/$D6,"")</f>
-      </c>
-      <c r="J6" s="56">
-        <f>IF($D6&gt;0,$D6-$H6,"")</f>
-      </c>
-      <c r="K6" s="59">
-        <f>IF($D6&gt;0,$J6/$D6,"")</f>
+      <c r="G6" s="58">
+        <f>IF($E6&gt;0,$F6/$E6,"")</f>
+      </c>
+      <c r="H6" s="57">
+        <f>ROUND($E6*'③ 고정비 설정'!$C$20,0)</f>
+      </c>
+      <c r="I6" s="57">
+        <f>ROUND($F6+$H6,0)</f>
+      </c>
+      <c r="J6" s="59">
+        <f>IF($E6&gt;0,$I6/$E6,"")</f>
+      </c>
+      <c r="K6" s="57">
+        <f>IF($E6&gt;0,$E6-$I6,"")</f>
       </c>
       <c r="L6" s="60">
-        <f>IF($D6&lt;=0,"⬜ 판매가 입력",IF($E6&lt;=0,"⬜ 재료 확인",IF($F6&lt;='③ 고정비 설정'!$C$17,"✅ 양호",IF($F6&lt;='③ 고정비 설정'!$C$18,"🟡 주의","🔴 과다"))))</f>
+        <f>IF($E6&gt;0,$K6/$E6,"")</f>
       </c>
       <c r="M6" s="61">
-        <f>IF($D6&gt;0,$F6+ROW()/1000000,"")</f>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="62">
+        <f>IF($D6&lt;=0,"⬜ 판매가 입력",IF($F6&lt;=0,"⬜ 재료 확인",IF($G6&lt;='③ 고정비 설정'!$C$21,"✅ 양호",IF($G6&lt;='③ 고정비 설정'!$C$22,"🟡 주의","🔴 과다"))))</f>
+      </c>
+      <c r="N6" s="62">
+        <f>IF($D6&gt;0,$G6+ROW()/1000000,"")</f>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="63">
         <v>2</v>
       </c>
-      <c r="B7" s="63" t="s">
-        <v>70</v>
+      <c r="B7" s="64" t="s">
+        <v>73</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D7" s="55">
         <v>5000</v>
       </c>
       <c r="E7" s="56">
+        <f>ROUND($D7/'③ 고정비 설정'!$C$17,0)</f>
+      </c>
+      <c r="F7" s="57">
         <f>ROUND(SUMIF('⑤ 레시피 상세'!$B$6:$B$20,$C7,'⑤ 레시피 상세'!$K$6:$K$20),1)</f>
       </c>
-      <c r="F7" s="57">
-        <f>IF($D7&gt;0,$E7/$D7,"")</f>
-      </c>
-      <c r="G7" s="56">
-        <f>ROUND($D7*'③ 고정비 설정'!$C$16,0)</f>
-      </c>
-      <c r="H7" s="56">
-        <f>ROUND($E7+$G7,0)</f>
-      </c>
-      <c r="I7" s="58">
-        <f>IF($D7&gt;0,$H7/$D7,"")</f>
-      </c>
-      <c r="J7" s="56">
-        <f>IF($D7&gt;0,$D7-$H7,"")</f>
-      </c>
-      <c r="K7" s="59">
-        <f>IF($D7&gt;0,$J7/$D7,"")</f>
+      <c r="G7" s="58">
+        <f>IF($E7&gt;0,$F7/$E7,"")</f>
+      </c>
+      <c r="H7" s="57">
+        <f>ROUND($E7*'③ 고정비 설정'!$C$20,0)</f>
+      </c>
+      <c r="I7" s="57">
+        <f>ROUND($F7+$H7,0)</f>
+      </c>
+      <c r="J7" s="59">
+        <f>IF($E7&gt;0,$I7/$E7,"")</f>
+      </c>
+      <c r="K7" s="57">
+        <f>IF($E7&gt;0,$E7-$I7,"")</f>
       </c>
       <c r="L7" s="60">
-        <f>IF($D7&lt;=0,"⬜ 판매가 입력",IF($E7&lt;=0,"⬜ 재료 확인",IF($F7&lt;='③ 고정비 설정'!$C$17,"✅ 양호",IF($F7&lt;='③ 고정비 설정'!$C$18,"🟡 주의","🔴 과다"))))</f>
+        <f>IF($E7&gt;0,$K7/$E7,"")</f>
       </c>
       <c r="M7" s="61">
-        <f>IF($D7&gt;0,$F7+ROW()/1000000,"")</f>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <f>IF($D7&lt;=0,"⬜ 판매가 입력",IF($F7&lt;=0,"⬜ 재료 확인",IF($G7&lt;='③ 고정비 설정'!$C$21,"✅ 양호",IF($G7&lt;='③ 고정비 설정'!$C$22,"🟡 주의","🔴 과다"))))</f>
+      </c>
+      <c r="N7" s="62">
+        <f>IF($D7&gt;0,$G7+ROW()/1000000,"")</f>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="53">
         <v>3</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D8" s="55">
         <v>12000</v>
       </c>
       <c r="E8" s="56">
+        <f>ROUND($D8/'③ 고정비 설정'!$C$17,0)</f>
+      </c>
+      <c r="F8" s="57">
         <f>ROUND(SUMIF('⑤ 레시피 상세'!$B$21:$B$22,$C8,'⑤ 레시피 상세'!$K$21:$K$22),1)</f>
       </c>
-      <c r="F8" s="57">
-        <f>IF($D8&gt;0,$E8/$D8,"")</f>
-      </c>
-      <c r="G8" s="56">
-        <f>ROUND($D8*'③ 고정비 설정'!$C$16,0)</f>
-      </c>
-      <c r="H8" s="56">
-        <f>ROUND($E8+$G8,0)</f>
-      </c>
-      <c r="I8" s="58">
-        <f>IF($D8&gt;0,$H8/$D8,"")</f>
-      </c>
-      <c r="J8" s="56">
-        <f>IF($D8&gt;0,$D8-$H8,"")</f>
-      </c>
-      <c r="K8" s="59">
-        <f>IF($D8&gt;0,$J8/$D8,"")</f>
+      <c r="G8" s="58">
+        <f>IF($E8&gt;0,$F8/$E8,"")</f>
+      </c>
+      <c r="H8" s="57">
+        <f>ROUND($E8*'③ 고정비 설정'!$C$20,0)</f>
+      </c>
+      <c r="I8" s="57">
+        <f>ROUND($F8+$H8,0)</f>
+      </c>
+      <c r="J8" s="59">
+        <f>IF($E8&gt;0,$I8/$E8,"")</f>
+      </c>
+      <c r="K8" s="57">
+        <f>IF($E8&gt;0,$E8-$I8,"")</f>
       </c>
       <c r="L8" s="60">
-        <f>IF($D8&lt;=0,"⬜ 판매가 입력",IF($E8&lt;=0,"⬜ 재료 확인",IF($F8&lt;='③ 고정비 설정'!$C$17,"✅ 양호",IF($F8&lt;='③ 고정비 설정'!$C$18,"🟡 주의","🔴 과다"))))</f>
+        <f>IF($E8&gt;0,$K8/$E8,"")</f>
       </c>
       <c r="M8" s="61">
-        <f>IF($D8&gt;0,$F8+ROW()/1000000,"")</f>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="64" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="65">
+        <f>IF($D8&lt;=0,"⬜ 판매가 입력",IF($F8&lt;=0,"⬜ 재료 확인",IF($G8&lt;='③ 고정비 설정'!$C$21,"✅ 양호",IF($G8&lt;='③ 고정비 설정'!$C$22,"🟡 주의","🔴 과다"))))</f>
+      </c>
+      <c r="N8" s="62">
+        <f>IF($D8&gt;0,$G8+ROW()/1000000,"")</f>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="65" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="65"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66">
         <f>SUM(D6:D8)</f>
       </c>
-      <c r="E9" s="65">
+      <c r="E9" s="66">
         <f>SUM(E6:E8)</f>
       </c>
       <c r="F9" s="66">
-        <f>IF(D9&gt;0,E9/D9,"")</f>
-      </c>
-      <c r="G9" s="65">
-        <f>SUM(G6:G8)</f>
-      </c>
-      <c r="H9" s="65">
+        <f>SUM(F6:F8)</f>
+      </c>
+      <c r="G9" s="67">
+        <f>IF(E9&gt;0,F9/E9,"")</f>
+      </c>
+      <c r="H9" s="66">
         <f>SUM(H6:H8)</f>
       </c>
       <c r="I9" s="66">
-        <f>IF(D9&gt;0,H9/D9,"")</f>
-      </c>
-      <c r="J9" s="65">
-        <f>IF(D9&gt;0,D9-H9,"")</f>
+        <f>SUM(I6:I8)</f>
+      </c>
+      <c r="J9" s="67">
+        <f>IF(E9&gt;0,I9/E9,"")</f>
       </c>
       <c r="K9" s="66">
-        <f>IF(D9&gt;0,J9/D9,"")</f>
+        <f>IF(E9&gt;0,E9-I9,"")</f>
       </c>
       <c r="L9" s="67">
-        <f>"✅"&amp;COUNTIF(L6:L8,"*양호*")&amp;"  🟡"&amp;COUNTIF(L6:L8,"*주의*")&amp;"  🔴"&amp;COUNTIF(L6:L8,"*과다*")</f>
-      </c>
-      <c r="M9" s="68"/>
+        <f>IF(E9&gt;0,K9/E9,"")</f>
+      </c>
+      <c r="M9" s="68">
+        <f>"✅"&amp;COUNTIF(M6:M8,"*양호*")&amp;"  🟡"&amp;COUNTIF(M6:M8,"*주의*")&amp;"  🔴"&amp;COUNTIF(M6:M8,"*과다*")</f>
+      </c>
+      <c r="N9" s="69"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:L8"/>
+  <autoFilter ref="A5:M8"/>
   <mergeCells count="4">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A3:N3"/>
     <mergeCell ref="A9:C9"/>
   </mergeCells>
-  <conditionalFormatting sqref="F6:F8">
+  <conditionalFormatting sqref="G6:G8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
-      <formula>'③ 고정비 설정'!$C$18</formula>
+      <formula>'③ 고정비 설정'!$C$22</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>'③ 고정비 설정'!$C$17</formula>
+      <formula>'③ 고정비 설정'!$C$21</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K8">
+  <conditionalFormatting sqref="L6:L8">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -2776,7 +2846,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2792,7 +2862,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2808,7 +2878,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
@@ -2824,686 +2894,686 @@
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L5" s="30" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="69" t="s">
-        <v>69</v>
+      <c r="A6" s="70" t="s">
+        <v>72</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C6" s="53">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
-        <v>103</v>
+      <c r="D6" s="71" t="s">
+        <v>106</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="F6" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="71">
+        <v>107</v>
+      </c>
+      <c r="F6" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="72">
         <v>200</v>
       </c>
       <c r="H6" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="I6" s="72">
+        <v>108</v>
+      </c>
+      <c r="I6" s="73">
         <v>1</v>
       </c>
-      <c r="J6" s="73">
+      <c r="J6" s="74">
         <f>IF($D6="무료",0,IF($D6="메뉴",0,IF($D6="프렙",IFERROR(VLOOKUP($E6,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E6,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
       </c>
-      <c r="K6" s="74">
+      <c r="K6" s="75">
         <f>IF($D6="메뉴",ROUND($G6*$J6,1),IF($I6&gt;0,ROUND($G6/$I6*$J6,1),0))</f>
       </c>
       <c r="L6" s="54" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="69" t="s">
-        <v>69</v>
+      <c r="A7" s="70" t="s">
+        <v>72</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C7" s="53">
         <v>2</v>
       </c>
-      <c r="D7" s="70" t="s">
-        <v>103</v>
+      <c r="D7" s="71" t="s">
+        <v>106</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="F7" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="71">
+        <v>110</v>
+      </c>
+      <c r="F7" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="72">
         <v>100</v>
       </c>
       <c r="H7" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="I7" s="72">
+        <v>108</v>
+      </c>
+      <c r="I7" s="73">
         <v>0.9</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="74">
         <f>IF($D7="무료",0,IF($D7="메뉴",0,IF($D7="프렙",IFERROR(VLOOKUP($E7,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E7,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
       </c>
-      <c r="K7" s="74">
+      <c r="K7" s="75">
         <f>IF($D7="메뉴",ROUND($G7*$J7,1),IF($I7&gt;0,ROUND($G7/$I7*$J7,1),0))</f>
       </c>
       <c r="L7" s="54" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="69" t="s">
-        <v>69</v>
+      <c r="A8" s="70" t="s">
+        <v>72</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C8" s="53">
         <v>3</v>
       </c>
-      <c r="D8" s="70" t="s">
-        <v>103</v>
+      <c r="D8" s="71" t="s">
+        <v>106</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="F8" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" s="71">
+        <v>112</v>
+      </c>
+      <c r="F8" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="72">
         <v>30</v>
       </c>
       <c r="H8" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="I8" s="72">
+        <v>108</v>
+      </c>
+      <c r="I8" s="73">
         <v>1</v>
       </c>
-      <c r="J8" s="73">
+      <c r="J8" s="74">
         <f>IF($D8="무료",0,IF($D8="메뉴",0,IF($D8="프렙",IFERROR(VLOOKUP($E8,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E8,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
       </c>
-      <c r="K8" s="74">
+      <c r="K8" s="75">
         <f>IF($D8="메뉴",ROUND($G8*$J8,1),IF($I8&gt;0,ROUND($G8/$I8*$J8,1),0))</f>
       </c>
       <c r="L8" s="54" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="69" t="s">
-        <v>69</v>
+      <c r="A9" s="70" t="s">
+        <v>72</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C9" s="53">
         <v>4</v>
       </c>
-      <c r="D9" s="70" t="s">
-        <v>103</v>
+      <c r="D9" s="71" t="s">
+        <v>106</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>111</v>
-      </c>
-      <c r="F9" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9" s="71">
+        <v>114</v>
+      </c>
+      <c r="F9" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="72">
         <v>20</v>
       </c>
       <c r="H9" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="I9" s="72">
+        <v>108</v>
+      </c>
+      <c r="I9" s="73">
         <v>1</v>
       </c>
-      <c r="J9" s="73">
+      <c r="J9" s="74">
         <f>IF($D9="무료",0,IF($D9="메뉴",0,IF($D9="프렙",IFERROR(VLOOKUP($E9,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E9,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
       </c>
-      <c r="K9" s="74">
+      <c r="K9" s="75">
         <f>IF($D9="메뉴",ROUND($G9*$J9,1),IF($I9&gt;0,ROUND($G9/$I9*$J9,1),0))</f>
       </c>
       <c r="L9" s="54" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="69" t="s">
-        <v>69</v>
+      <c r="A10" s="70" t="s">
+        <v>72</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C10" s="53">
         <v>5</v>
       </c>
-      <c r="D10" s="70" t="s">
-        <v>103</v>
+      <c r="D10" s="71" t="s">
+        <v>106</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="F10" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" s="71">
+        <v>115</v>
+      </c>
+      <c r="F10" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="72">
         <v>15</v>
       </c>
       <c r="H10" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="I10" s="72">
+        <v>108</v>
+      </c>
+      <c r="I10" s="73">
         <v>1</v>
       </c>
-      <c r="J10" s="73">
+      <c r="J10" s="74">
         <f>IF($D10="무료",0,IF($D10="메뉴",0,IF($D10="프렙",IFERROR(VLOOKUP($E10,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E10,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
       </c>
-      <c r="K10" s="74">
+      <c r="K10" s="75">
         <f>IF($D10="메뉴",ROUND($G10*$J10,1),IF($I10&gt;0,ROUND($G10/$I10*$J10,1),0))</f>
       </c>
       <c r="L10" s="54" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="69" t="s">
-        <v>69</v>
+      <c r="A11" s="70" t="s">
+        <v>72</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C11" s="53">
         <v>6</v>
       </c>
-      <c r="D11" s="70" t="s">
-        <v>103</v>
+      <c r="D11" s="71" t="s">
+        <v>106</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>113</v>
-      </c>
-      <c r="F11" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="71">
+        <v>116</v>
+      </c>
+      <c r="F11" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="72">
         <v>3</v>
       </c>
       <c r="H11" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="I11" s="72">
+        <v>108</v>
+      </c>
+      <c r="I11" s="73">
         <v>1</v>
       </c>
-      <c r="J11" s="73">
+      <c r="J11" s="74">
         <f>IF($D11="무료",0,IF($D11="메뉴",0,IF($D11="프렙",IFERROR(VLOOKUP($E11,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E11,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
       </c>
-      <c r="K11" s="74">
+      <c r="K11" s="75">
         <f>IF($D11="메뉴",ROUND($G11*$J11,1),IF($I11&gt;0,ROUND($G11/$I11*$J11,1),0))</f>
       </c>
       <c r="L11" s="54" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="69" t="s">
-        <v>69</v>
+      <c r="A12" s="70" t="s">
+        <v>72</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C12" s="53">
         <v>7</v>
       </c>
-      <c r="D12" s="70" t="s">
-        <v>103</v>
+      <c r="D12" s="71" t="s">
+        <v>106</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="F12" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="71">
+        <v>117</v>
+      </c>
+      <c r="F12" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="72">
         <v>1</v>
       </c>
       <c r="H12" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="I12" s="72">
+        <v>108</v>
+      </c>
+      <c r="I12" s="73">
         <v>1</v>
       </c>
-      <c r="J12" s="73">
+      <c r="J12" s="74">
         <f>IF($D12="무료",0,IF($D12="메뉴",0,IF($D12="프렙",IFERROR(VLOOKUP($E12,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E12,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
       </c>
-      <c r="K12" s="74">
+      <c r="K12" s="75">
         <f>IF($D12="메뉴",ROUND($G12*$J12,1),IF($I12&gt;0,ROUND($G12/$I12*$J12,1),0))</f>
       </c>
       <c r="L12" s="54" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="69" t="s">
-        <v>69</v>
+      <c r="A13" s="70" t="s">
+        <v>72</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C13" s="53">
         <v>8</v>
       </c>
-      <c r="D13" s="70" t="s">
-        <v>103</v>
+      <c r="D13" s="71" t="s">
+        <v>106</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="F13" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="71">
+        <v>118</v>
+      </c>
+      <c r="F13" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="72">
         <v>10</v>
       </c>
       <c r="H13" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="I13" s="72">
+        <v>108</v>
+      </c>
+      <c r="I13" s="73">
         <v>1</v>
       </c>
-      <c r="J13" s="73">
+      <c r="J13" s="74">
         <f>IF($D13="무료",0,IF($D13="메뉴",0,IF($D13="프렙",IFERROR(VLOOKUP($E13,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E13,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
       </c>
-      <c r="K13" s="74">
+      <c r="K13" s="75">
         <f>IF($D13="메뉴",ROUND($G13*$J13,1),IF($I13&gt;0,ROUND($G13/$I13*$J13,1),0))</f>
       </c>
       <c r="L13" s="54" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="69" t="s">
-        <v>69</v>
+      <c r="A14" s="70" t="s">
+        <v>72</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C14" s="53">
         <v>9</v>
       </c>
-      <c r="D14" s="75" t="s">
-        <v>117</v>
+      <c r="D14" s="76" t="s">
+        <v>120</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="F14" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" s="71">
+        <v>121</v>
+      </c>
+      <c r="F14" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="72">
         <v>40</v>
       </c>
       <c r="H14" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="I14" s="72">
+        <v>108</v>
+      </c>
+      <c r="I14" s="73">
         <v>1</v>
       </c>
-      <c r="J14" s="73">
+      <c r="J14" s="74">
         <f>IF($D14="무료",0,IF($D14="메뉴",0,IF($D14="프렙",IFERROR(VLOOKUP($E14,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E14,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
       </c>
-      <c r="K14" s="74">
+      <c r="K14" s="75">
         <f>IF($D14="메뉴",ROUND($G14*$J14,1),IF($I14&gt;0,ROUND($G14/$I14*$J14,1),0))</f>
       </c>
       <c r="L14" s="54" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="76" t="s">
-        <v>70</v>
+      <c r="A15" s="77" t="s">
+        <v>73</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="62">
+        <v>90</v>
+      </c>
+      <c r="C15" s="63">
         <v>1</v>
       </c>
-      <c r="D15" s="77" t="s">
-        <v>103</v>
+      <c r="D15" s="78" t="s">
+        <v>106</v>
       </c>
       <c r="E15" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="72">
+        <v>150</v>
+      </c>
+      <c r="H15" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="I15" s="73">
+        <v>0.85</v>
+      </c>
+      <c r="J15" s="74">
+        <f>IF($D15="무료",0,IF($D15="메뉴",0,IF($D15="프렙",IFERROR(VLOOKUP($E15,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E15,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+      </c>
+      <c r="K15" s="75">
+        <f>IF($D15="메뉴",ROUND($G15*$J15,1),IF($I15&gt;0,ROUND($G15/$I15*$J15,1),0))</f>
+      </c>
+      <c r="L15" s="64" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="63">
+        <v>2</v>
+      </c>
+      <c r="D16" s="78" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="72">
+        <v>30</v>
+      </c>
+      <c r="H16" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="I16" s="73">
+        <v>1</v>
+      </c>
+      <c r="J16" s="74">
+        <f>IF($D16="무료",0,IF($D16="메뉴",0,IF($D16="프렙",IFERROR(VLOOKUP($E16,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E16,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+      </c>
+      <c r="K16" s="75">
+        <f>IF($D16="메뉴",ROUND($G16*$J16,1),IF($I16&gt;0,ROUND($G16/$I16*$J16,1),0))</f>
+      </c>
+      <c r="L16" s="64" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="63">
+        <v>3</v>
+      </c>
+      <c r="D17" s="78" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="F17" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="72">
         <v>120</v>
       </c>
-      <c r="F15" s="76" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="71">
-        <v>150</v>
-      </c>
-      <c r="H15" s="62" t="s">
-        <v>105</v>
-      </c>
-      <c r="I15" s="72">
-        <v>0.85</v>
-      </c>
-      <c r="J15" s="73">
-        <f>IF($D15="무료",0,IF($D15="메뉴",0,IF($D15="프렙",IFERROR(VLOOKUP($E15,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E15,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
-      </c>
-      <c r="K15" s="74">
-        <f>IF($D15="메뉴",ROUND($G15*$J15,1),IF($I15&gt;0,ROUND($G15/$I15*$J15,1),0))</f>
-      </c>
-      <c r="L15" s="63" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="76" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="62">
-        <v>2</v>
-      </c>
-      <c r="D16" s="77" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" s="49" t="s">
-        <v>109</v>
-      </c>
-      <c r="F16" s="76" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="71">
-        <v>30</v>
-      </c>
-      <c r="H16" s="62" t="s">
-        <v>105</v>
-      </c>
-      <c r="I16" s="72">
+      <c r="H17" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="I17" s="73">
         <v>1</v>
       </c>
-      <c r="J16" s="73">
-        <f>IF($D16="무료",0,IF($D16="메뉴",0,IF($D16="프렙",IFERROR(VLOOKUP($E16,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E16,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
-      </c>
-      <c r="K16" s="74">
-        <f>IF($D16="메뉴",ROUND($G16*$J16,1),IF($I16&gt;0,ROUND($G16/$I16*$J16,1),0))</f>
-      </c>
-      <c r="L16" s="63" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="76" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" s="62">
+      <c r="J17" s="74">
+        <f>IF($D17="무료",0,IF($D17="메뉴",0,IF($D17="프렙",IFERROR(VLOOKUP($E17,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E17,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+      </c>
+      <c r="K17" s="75">
+        <f>IF($D17="메뉴",ROUND($G17*$J17,1),IF($I17&gt;0,ROUND($G17/$I17*$J17,1),0))</f>
+      </c>
+      <c r="L17" s="64" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="63">
+        <v>4</v>
+      </c>
+      <c r="D18" s="78" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>127</v>
+      </c>
+      <c r="F18" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="72">
+        <v>10</v>
+      </c>
+      <c r="H18" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="73">
+        <v>1</v>
+      </c>
+      <c r="J18" s="74">
+        <f>IF($D18="무료",0,IF($D18="메뉴",0,IF($D18="프렙",IFERROR(VLOOKUP($E18,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E18,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+      </c>
+      <c r="K18" s="75">
+        <f>IF($D18="메뉴",ROUND($G18*$J18,1),IF($I18&gt;0,ROUND($G18/$I18*$J18,1),0))</f>
+      </c>
+      <c r="L18" s="64" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="63">
+        <v>5</v>
+      </c>
+      <c r="D19" s="78" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="F19" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="72">
         <v>3</v>
       </c>
-      <c r="D17" s="77" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" s="49" t="s">
-        <v>122</v>
-      </c>
-      <c r="F17" s="76" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17" s="71">
-        <v>120</v>
-      </c>
-      <c r="H17" s="62" t="s">
-        <v>105</v>
-      </c>
-      <c r="I17" s="72">
+      <c r="H19" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" s="73">
         <v>1</v>
       </c>
-      <c r="J17" s="73">
-        <f>IF($D17="무료",0,IF($D17="메뉴",0,IF($D17="프렙",IFERROR(VLOOKUP($E17,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E17,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
-      </c>
-      <c r="K17" s="74">
-        <f>IF($D17="메뉴",ROUND($G17*$J17,1),IF($I17&gt;0,ROUND($G17/$I17*$J17,1),0))</f>
-      </c>
-      <c r="L17" s="63" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="76" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" s="62">
-        <v>4</v>
-      </c>
-      <c r="D18" s="77" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" s="49" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" s="76" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18" s="71">
-        <v>10</v>
-      </c>
-      <c r="H18" s="62" t="s">
-        <v>105</v>
-      </c>
-      <c r="I18" s="72">
+      <c r="J19" s="74">
+        <f>IF($D19="무료",0,IF($D19="메뉴",0,IF($D19="프렙",IFERROR(VLOOKUP($E19,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E19,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+      </c>
+      <c r="K19" s="75">
+        <f>IF($D19="메뉴",ROUND($G19*$J19,1),IF($I19&gt;0,ROUND($G19/$I19*$J19,1),0))</f>
+      </c>
+      <c r="L19" s="64" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="63">
+        <v>6</v>
+      </c>
+      <c r="D20" s="79" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="72">
+        <v>100</v>
+      </c>
+      <c r="H20" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" s="73">
         <v>1</v>
       </c>
-      <c r="J18" s="73">
-        <f>IF($D18="무료",0,IF($D18="메뉴",0,IF($D18="프렙",IFERROR(VLOOKUP($E18,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E18,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
-      </c>
-      <c r="K18" s="74">
-        <f>IF($D18="메뉴",ROUND($G18*$J18,1),IF($I18&gt;0,ROUND($G18/$I18*$J18,1),0))</f>
-      </c>
-      <c r="L18" s="63" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="76" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" s="62">
-        <v>5</v>
-      </c>
-      <c r="D19" s="77" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="F19" s="76" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" s="71">
-        <v>3</v>
-      </c>
-      <c r="H19" s="62" t="s">
-        <v>105</v>
-      </c>
-      <c r="I19" s="72">
-        <v>1</v>
-      </c>
-      <c r="J19" s="73">
-        <f>IF($D19="무료",0,IF($D19="메뉴",0,IF($D19="프렙",IFERROR(VLOOKUP($E19,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E19,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
-      </c>
-      <c r="K19" s="74">
-        <f>IF($D19="메뉴",ROUND($G19*$J19,1),IF($I19&gt;0,ROUND($G19/$I19*$J19,1),0))</f>
-      </c>
-      <c r="L19" s="63" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="76" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" s="62">
-        <v>6</v>
-      </c>
-      <c r="D20" s="78" t="s">
-        <v>125</v>
-      </c>
-      <c r="E20" s="49" t="s">
-        <v>126</v>
-      </c>
-      <c r="F20" s="76" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20" s="71">
-        <v>100</v>
-      </c>
-      <c r="H20" s="62" t="s">
-        <v>105</v>
-      </c>
-      <c r="I20" s="72">
-        <v>1</v>
-      </c>
-      <c r="J20" s="73">
+      <c r="J20" s="74">
         <f>IF($D20="무료",0,IF($D20="메뉴",0,IF($D20="프렙",IFERROR(VLOOKUP($E20,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E20,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
       </c>
-      <c r="K20" s="74">
+      <c r="K20" s="75">
         <f>IF($D20="메뉴",ROUND($G20*$J20,1),IF($I20&gt;0,ROUND($G20/$I20*$J20,1),0))</f>
       </c>
-      <c r="L20" s="63" t="s">
-        <v>127</v>
+      <c r="L20" s="64" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="69" t="s">
-        <v>71</v>
+      <c r="A21" s="70" t="s">
+        <v>74</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C21" s="53">
         <v>1</v>
       </c>
-      <c r="D21" s="79" t="s">
-        <v>128</v>
+      <c r="D21" s="80" t="s">
+        <v>131</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" s="71">
+        <v>89</v>
+      </c>
+      <c r="F21" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="72">
         <v>1</v>
       </c>
       <c r="H21" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="I21" s="72">
+        <v>132</v>
+      </c>
+      <c r="I21" s="73">
         <v>1</v>
       </c>
-      <c r="J21" s="73">
-        <f>IF($D21="무료",0,IF($D21="메뉴",IFERROR(VLOOKUP($E21,'④ 메뉴 원가표'!$C$6:$F$7,3,FALSE),0),IF($D21="프렙",IFERROR(VLOOKUP($E21,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E21,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
-      </c>
-      <c r="K21" s="74">
+      <c r="J21" s="74">
+        <f>IF($D21="무료",0,IF($D21="메뉴",IFERROR(VLOOKUP($E21,'④ 메뉴 원가표'!$C$6:$F$7,4,FALSE),0),IF($D21="프렙",IFERROR(VLOOKUP($E21,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E21,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+      </c>
+      <c r="K21" s="75">
         <f>IF($D21="메뉴",ROUND($G21*$J21,1),IF($I21&gt;0,ROUND($G21/$I21*$J21,1),0))</f>
       </c>
       <c r="L21" s="54" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="69" t="s">
-        <v>71</v>
+      <c r="A22" s="70" t="s">
+        <v>74</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C22" s="53">
         <v>2</v>
       </c>
-      <c r="D22" s="79" t="s">
-        <v>128</v>
+      <c r="D22" s="80" t="s">
+        <v>131</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="F22" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22" s="71">
+        <v>90</v>
+      </c>
+      <c r="F22" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="72">
         <v>1</v>
       </c>
       <c r="H22" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="I22" s="72">
+        <v>132</v>
+      </c>
+      <c r="I22" s="73">
         <v>1</v>
       </c>
-      <c r="J22" s="73">
-        <f>IF($D22="무료",0,IF($D22="메뉴",IFERROR(VLOOKUP($E22,'④ 메뉴 원가표'!$C$6:$F$7,3,FALSE),0),IF($D22="프렙",IFERROR(VLOOKUP($E22,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E22,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
-      </c>
-      <c r="K22" s="74">
+      <c r="J22" s="74">
+        <f>IF($D22="무료",0,IF($D22="메뉴",IFERROR(VLOOKUP($E22,'④ 메뉴 원가표'!$C$6:$F$7,4,FALSE),0),IF($D22="프렙",IFERROR(VLOOKUP($E22,'② 프렙 원가'!$B$6:$F$6,5,FALSE),0),IFERROR(VLOOKUP($E22,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0))))</f>
+      </c>
+      <c r="K22" s="75">
         <f>IF($D22="메뉴",ROUND($G22*$J22,1),IF($I22&gt;0,ROUND($G22/$I22*$J22,1),0))</f>
       </c>
       <c r="L22" s="54" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -3558,7 +3628,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3570,7 +3640,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
@@ -3582,28 +3652,28 @@
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -3611,51 +3681,51 @@
         <v>1</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C6" s="55">
         <v>12000</v>
       </c>
-      <c r="D6" s="80">
+      <c r="D6" s="81">
         <v>1</v>
       </c>
       <c r="E6" s="53" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F6" s="55">
         <v>1000</v>
       </c>
-      <c r="G6" s="81">
+      <c r="G6" s="82">
         <f>IF(F6&gt;0,C6/F6,0)</f>
       </c>
-      <c r="H6" s="82" t="s">
-        <v>59</v>
+      <c r="H6" s="83" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="62">
+      <c r="A7" s="63">
         <v>2</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C7" s="55">
         <v>62000</v>
       </c>
-      <c r="D7" s="80">
+      <c r="D7" s="81">
         <v>20</v>
       </c>
-      <c r="E7" s="62" t="s">
-        <v>137</v>
+      <c r="E7" s="63" t="s">
+        <v>140</v>
       </c>
       <c r="F7" s="55">
         <v>20000</v>
       </c>
-      <c r="G7" s="81">
+      <c r="G7" s="82">
         <f>IF(F7&gt;0,C7/F7,0)</f>
       </c>
-      <c r="H7" s="83" t="s">
-        <v>59</v>
+      <c r="H7" s="84" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -3663,51 +3733,51 @@
         <v>3</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C8" s="55">
         <v>14000</v>
       </c>
-      <c r="D8" s="80">
+      <c r="D8" s="81">
         <v>15</v>
       </c>
       <c r="E8" s="53" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F8" s="55">
         <v>15000</v>
       </c>
-      <c r="G8" s="81">
+      <c r="G8" s="82">
         <f>IF(F8&gt;0,C8/F8,0)</f>
       </c>
-      <c r="H8" s="82" t="s">
-        <v>59</v>
+      <c r="H8" s="83" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="62">
+      <c r="A9" s="63">
         <v>4</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C9" s="55">
         <v>16500</v>
       </c>
-      <c r="D9" s="80">
+      <c r="D9" s="81">
         <v>3</v>
       </c>
-      <c r="E9" s="62" t="s">
-        <v>137</v>
+      <c r="E9" s="63" t="s">
+        <v>140</v>
       </c>
       <c r="F9" s="55">
         <v>3000</v>
       </c>
-      <c r="G9" s="81">
+      <c r="G9" s="82">
         <f>IF(F9&gt;0,C9/F9,0)</f>
       </c>
-      <c r="H9" s="83" t="s">
-        <v>59</v>
+      <c r="H9" s="84" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3715,51 +3785,51 @@
         <v>5</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C10" s="55">
         <v>35000</v>
       </c>
-      <c r="D10" s="80">
+      <c r="D10" s="81">
         <v>20</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F10" s="55">
         <v>20000</v>
       </c>
-      <c r="G10" s="81">
+      <c r="G10" s="82">
         <f>IF(F10&gt;0,C10/F10,0)</f>
       </c>
-      <c r="H10" s="82" t="s">
-        <v>59</v>
+      <c r="H10" s="83" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="62">
+      <c r="A11" s="63">
         <v>6</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C11" s="55">
         <v>1650</v>
       </c>
-      <c r="D11" s="80">
+      <c r="D11" s="81">
         <v>1</v>
       </c>
-      <c r="E11" s="62" t="s">
-        <v>138</v>
+      <c r="E11" s="63" t="s">
+        <v>141</v>
       </c>
       <c r="F11" s="55">
         <v>1000</v>
       </c>
-      <c r="G11" s="81">
+      <c r="G11" s="82">
         <f>IF(F11&gt;0,C11/F11,0)</f>
       </c>
-      <c r="H11" s="83" t="s">
-        <v>59</v>
+      <c r="H11" s="84" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -3767,51 +3837,51 @@
         <v>7</v>
       </c>
       <c r="B12" s="44" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C12" s="55">
         <v>14500</v>
       </c>
-      <c r="D12" s="80">
+      <c r="D12" s="81">
         <v>13.1</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F12" s="55">
         <v>13100</v>
       </c>
-      <c r="G12" s="81">
+      <c r="G12" s="82">
         <f>IF(F12&gt;0,C12/F12,0)</f>
       </c>
-      <c r="H12" s="82" t="s">
-        <v>59</v>
+      <c r="H12" s="83" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="62">
+      <c r="A13" s="63">
         <v>8</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C13" s="55">
         <v>49500</v>
       </c>
-      <c r="D13" s="80">
+      <c r="D13" s="81">
         <v>18</v>
       </c>
-      <c r="E13" s="62" t="s">
-        <v>138</v>
+      <c r="E13" s="63" t="s">
+        <v>141</v>
       </c>
       <c r="F13" s="55">
         <v>18000</v>
       </c>
-      <c r="G13" s="81">
+      <c r="G13" s="82">
         <f>IF(F13&gt;0,C13/F13,0)</f>
       </c>
-      <c r="H13" s="83" t="s">
-        <v>59</v>
+      <c r="H13" s="84" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -3819,51 +3889,51 @@
         <v>9</v>
       </c>
       <c r="B14" s="44" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C14" s="55">
         <v>5500</v>
       </c>
-      <c r="D14" s="80">
+      <c r="D14" s="81">
         <v>1.8</v>
       </c>
       <c r="E14" s="53" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F14" s="55">
         <v>1800</v>
       </c>
-      <c r="G14" s="81">
+      <c r="G14" s="82">
         <f>IF(F14&gt;0,C14/F14,0)</f>
       </c>
-      <c r="H14" s="82" t="s">
-        <v>59</v>
+      <c r="H14" s="83" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="62">
+      <c r="A15" s="63">
         <v>10</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C15" s="55">
         <v>15000</v>
       </c>
-      <c r="D15" s="80">
+      <c r="D15" s="81">
         <v>15</v>
       </c>
-      <c r="E15" s="62" t="s">
-        <v>137</v>
+      <c r="E15" s="63" t="s">
+        <v>140</v>
       </c>
       <c r="F15" s="55">
         <v>15000</v>
       </c>
-      <c r="G15" s="81">
+      <c r="G15" s="82">
         <f>IF(F15&gt;0,C15/F15,0)</f>
       </c>
-      <c r="H15" s="83" t="s">
-        <v>59</v>
+      <c r="H15" s="84" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3871,51 +3941,51 @@
         <v>11</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C16" s="55">
         <v>9000</v>
       </c>
-      <c r="D16" s="80">
+      <c r="D16" s="81">
         <v>0.4</v>
       </c>
       <c r="E16" s="53" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F16" s="55">
         <v>400</v>
       </c>
-      <c r="G16" s="81">
+      <c r="G16" s="82">
         <f>IF(F16&gt;0,C16/F16,0)</f>
       </c>
-      <c r="H16" s="82" t="s">
-        <v>59</v>
+      <c r="H16" s="83" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="62">
+      <c r="A17" s="63">
         <v>12</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C17" s="55">
         <v>4980</v>
       </c>
-      <c r="D17" s="80">
+      <c r="D17" s="81">
         <v>0.5</v>
       </c>
-      <c r="E17" s="62" t="s">
-        <v>137</v>
+      <c r="E17" s="63" t="s">
+        <v>140</v>
       </c>
       <c r="F17" s="55">
         <v>500</v>
       </c>
-      <c r="G17" s="81">
+      <c r="G17" s="82">
         <f>IF(F17&gt;0,C17/F17,0)</f>
       </c>
-      <c r="H17" s="83" t="s">
-        <v>59</v>
+      <c r="H17" s="84" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -3950,7 +4020,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3962,7 +4032,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3974,7 +4044,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
@@ -3986,28 +4056,28 @@
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -4015,30 +4085,30 @@
         <v>1</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C6" s="55">
         <v>1200</v>
       </c>
-      <c r="D6" s="72">
+      <c r="D6" s="73">
         <v>0.8</v>
       </c>
-      <c r="E6" s="56">
+      <c r="E6" s="57">
         <f>SUMIF($A$11:$A$14,$B6,$F$11:$F$14)</f>
       </c>
-      <c r="F6" s="81">
+      <c r="F6" s="82">
         <f>IF(C6&gt;0,E6/C6,0)</f>
       </c>
-      <c r="G6" s="56">
+      <c r="G6" s="57">
         <f>SUMIF($A$11:$A$14,$B6,$D$11:$D$14)</f>
       </c>
       <c r="H6" s="44" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -4050,107 +4120,107 @@
     </row>
     <row r="10" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B11" s="53" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D11" s="55">
         <v>1000</v>
       </c>
-      <c r="E11" s="73">
+      <c r="E11" s="74">
         <f>IFERROR(VLOOKUP($C11,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0)</f>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="57">
         <f>ROUND($D11*$E11,2)</f>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="44" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B12" s="53" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D12" s="55">
         <v>300</v>
       </c>
-      <c r="E12" s="73">
+      <c r="E12" s="74">
         <f>IFERROR(VLOOKUP($C12,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0)</f>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="57">
         <f>ROUND($D12*$E12,2)</f>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D13" s="55">
         <v>200</v>
       </c>
-      <c r="E13" s="73">
+      <c r="E13" s="74">
         <f>IFERROR(VLOOKUP($C13,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0)</f>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="57">
         <f>ROUND($D13*$E13,2)</f>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B14" s="53" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D14" s="55">
         <v>50</v>
       </c>
-      <c r="E14" s="73">
+      <c r="E14" s="74">
         <f>IFERROR(VLOOKUP($C14,'① 식재료 단가'!$B$6:$G$17,6,FALSE),0)</f>
       </c>
-      <c r="F14" s="56">
+      <c r="F14" s="57">
         <f>ROUND($D14*$E14,2)</f>
       </c>
     </row>
@@ -4172,7 +4242,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="19" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4193,7 +4263,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4202,7 +4272,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
@@ -4211,19 +4281,19 @@
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4231,33 +4301,33 @@
         <v>1</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C6" s="55">
         <v>8000000</v>
       </c>
-      <c r="D6" s="84" t="s">
-        <v>158</v>
+      <c r="D6" s="85" t="s">
+        <v>161</v>
       </c>
       <c r="E6" s="54" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="62">
+      <c r="A7" s="63">
         <v>2</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C7" s="55">
         <v>3000000</v>
       </c>
-      <c r="D7" s="84" t="s">
-        <v>158</v>
-      </c>
-      <c r="E7" s="63" t="s">
+      <c r="D7" s="85" t="s">
         <v>161</v>
+      </c>
+      <c r="E7" s="64" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -4265,33 +4335,33 @@
         <v>3</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C8" s="55">
         <v>800000</v>
       </c>
-      <c r="D8" s="84" t="s">
-        <v>158</v>
+      <c r="D8" s="85" t="s">
+        <v>161</v>
       </c>
       <c r="E8" s="54" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="62">
+      <c r="A9" s="63">
         <v>4</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C9" s="55">
         <v>1500000</v>
       </c>
-      <c r="D9" s="84" t="s">
-        <v>158</v>
-      </c>
-      <c r="E9" s="63" t="s">
-        <v>165</v>
+      <c r="D9" s="85" t="s">
+        <v>161</v>
+      </c>
+      <c r="E9" s="64" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -4299,47 +4369,47 @@
         <v>5</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C10" s="55">
         <v>6000000</v>
       </c>
-      <c r="D10" s="84" t="s">
-        <v>167</v>
-      </c>
-      <c r="E10" s="82" t="s">
-        <v>168</v>
+      <c r="D10" s="85" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" s="83" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="85" t="s">
-        <v>169</v>
-      </c>
-      <c r="B11" s="85"/>
-      <c r="C11" s="86">
+      <c r="A11" s="86" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="86"/>
+      <c r="C11" s="87">
         <f>SUM(C6:C10)</f>
       </c>
-      <c r="D11" s="87"/>
-      <c r="E11" s="88" t="s">
-        <v>170</v>
+      <c r="D11" s="88"/>
+      <c r="E11" s="89" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="85" t="s">
-        <v>171</v>
-      </c>
-      <c r="B12" s="85"/>
-      <c r="C12" s="86">
+      <c r="A12" s="86" t="s">
+        <v>174</v>
+      </c>
+      <c r="B12" s="86"/>
+      <c r="C12" s="87">
         <f>SUMIF(D6:D10,"포함",C6:C10)</f>
       </c>
-      <c r="D12" s="87"/>
-      <c r="E12" s="88" t="s">
-        <v>172</v>
+      <c r="D12" s="88"/>
+      <c r="E12" s="89" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -4347,59 +4417,111 @@
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="89" t="s">
-        <v>174</v>
-      </c>
-      <c r="B15" s="89"/>
-      <c r="C15" s="55">
-        <v>30000000</v>
+      <c r="A15" s="90" t="s">
+        <v>177</v>
+      </c>
+      <c r="B15" s="90"/>
+      <c r="C15" s="85" t="s">
+        <v>161</v>
       </c>
       <c r="D15" s="44"/>
       <c r="E15" s="54" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="89" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="89"/>
-      <c r="C16" s="58">
-        <f>IF(C15&gt;0,C12/C15,0)</f>
+      <c r="A16" s="90" t="s">
+        <v>179</v>
+      </c>
+      <c r="B16" s="90"/>
+      <c r="C16" s="73">
+        <v>0.1</v>
       </c>
       <c r="D16" s="44"/>
       <c r="E16" s="54" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="89" t="s">
-        <v>177</v>
-      </c>
-      <c r="B17" s="89"/>
-      <c r="C17" s="72">
-        <v>0.3</v>
+      <c r="A17" s="90" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="90"/>
+      <c r="C17" s="91">
+        <f>IF(C15="포함",1+C16,1)</f>
       </c>
       <c r="D17" s="44"/>
       <c r="E17" s="54" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="89" t="s">
-        <v>179</v>
-      </c>
-      <c r="B18" s="89"/>
-      <c r="C18" s="72">
-        <v>0.38</v>
+      <c r="A18" s="90" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="90"/>
+      <c r="C18" s="55">
+        <v>30000000</v>
       </c>
       <c r="D18" s="44"/>
       <c r="E18" s="54" t="s">
-        <v>180</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="90" t="s">
+        <v>185</v>
+      </c>
+      <c r="B19" s="90"/>
+      <c r="C19" s="57">
+        <f>ROUND(C18/C17,0)</f>
+      </c>
+      <c r="D19" s="44"/>
+      <c r="E19" s="54" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="90" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="90"/>
+      <c r="C20" s="59">
+        <f>IF(C19&gt;0,C12/C19,0)</f>
+      </c>
+      <c r="D20" s="44"/>
+      <c r="E20" s="54" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="90" t="s">
+        <v>188</v>
+      </c>
+      <c r="B21" s="90"/>
+      <c r="C21" s="73">
+        <v>0.3</v>
+      </c>
+      <c r="D21" s="44"/>
+      <c r="E21" s="54" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="90" t="s">
+        <v>190</v>
+      </c>
+      <c r="B22" s="90"/>
+      <c r="C22" s="73">
+        <v>0.38</v>
+      </c>
+      <c r="D22" s="44"/>
+      <c r="E22" s="54" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="14">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
@@ -4410,8 +4532,15 @@
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="입력 오류" error="포함 또는 별도 중에서 선택하세요." sqref="C15">
+      <formula1>"포함,별도"</formula1>
+    </dataValidation>
     <dataValidation type="list" showErrorMessage="1" errorTitle="입력 오류" error="포함 또는 제외 중에서 선택하세요." sqref="D10">
       <formula1>"포함,제외"</formula1>
     </dataValidation>
@@ -4440,7 +4569,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4449,7 +4578,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4458,155 +4587,155 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="53">
         <v>1</v>
       </c>
-      <c r="B5" s="90" t="s">
-        <v>186</v>
+      <c r="B5" s="92" t="s">
+        <v>197</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D5" s="44" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="62">
+      <c r="A6" s="63">
         <v>2</v>
       </c>
-      <c r="B6" s="91" t="s">
-        <v>186</v>
+      <c r="B6" s="93" t="s">
+        <v>197</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="E6" s="63" t="s">
-        <v>191</v>
+        <v>201</v>
+      </c>
+      <c r="E6" s="64" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="53">
         <v>3</v>
       </c>
-      <c r="B7" s="90" t="s">
-        <v>186</v>
+      <c r="B7" s="92" t="s">
+        <v>197</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D7" s="44" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="E7" s="54" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="62">
+      <c r="A8" s="63">
         <v>4</v>
       </c>
-      <c r="B8" s="91" t="s">
-        <v>186</v>
+      <c r="B8" s="93" t="s">
+        <v>197</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="E8" s="63" t="s">
-        <v>195</v>
+        <v>205</v>
+      </c>
+      <c r="E8" s="64" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="53">
         <v>5</v>
       </c>
-      <c r="B9" s="90" t="s">
-        <v>186</v>
+      <c r="B9" s="92" t="s">
+        <v>197</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="E9" s="54" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="62">
+      <c r="A10" s="63">
         <v>6</v>
       </c>
-      <c r="B10" s="91" t="s">
-        <v>198</v>
+      <c r="B10" s="93" t="s">
+        <v>209</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D10" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="E10" s="63" t="s">
-        <v>200</v>
+        <v>210</v>
+      </c>
+      <c r="E10" s="64" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="53">
         <v>7</v>
       </c>
-      <c r="B11" s="90" t="s">
-        <v>198</v>
+      <c r="B11" s="92" t="s">
+        <v>209</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="E11" s="54" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="62">
+      <c r="A12" s="63">
         <v>8</v>
       </c>
-      <c r="B12" s="91" t="s">
-        <v>198</v>
+      <c r="B12" s="93" t="s">
+        <v>209</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D12" s="49" t="s">
-        <v>203</v>
-      </c>
-      <c r="E12" s="63" t="s">
-        <v>204</v>
+        <v>214</v>
+      </c>
+      <c r="E12" s="64" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
